--- a/practice/module-2-sales-data.xlsx
+++ b/practice/module-2-sales-data.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Raw Sales" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Targets" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Tasks" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Solutions" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +46,27 @@
       <i val="1"/>
       <color rgb="00666666"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00555555"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -56,6 +76,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="000F6F3F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -83,6 +108,20 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2424,7 +2463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2629,6 +2668,402 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Create a Named Range called 'NorthTarget' that points to the Q1 North target on the Targets sheet (the cell with value 12000). Then write =NorthTarget in any cell to confirm it returns 12000.</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>2.6 Named Ranges</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Formulas → Define Name. Refers to: =Targets!$B$4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Convert the Targets table on the Targets sheet (A3:C8) to an Excel Table named 'tblTargets'. Verify the table name in Table Design.</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>2.12 Excel Tables</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Select A3:C8 → Ctrl+T → check 'My table has headers' → Table Design → Table Name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Open Power Query (Data → Get Data → From Other Sources → Blank Query, OR Data → From Table/Range on tblSales). In the editor: (a) Filter Status to remove 'Cancelled', (b) Add Custom Column 'Revenue' = [Quantity] * [Unit Price], (c) Group by Region with Sum of Revenue. Close &amp; Load to a new sheet.</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>2.14 Power Query</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Home → Close &amp; Load. The output sheet should have one row per region with totals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Use Linked Data Types: in cells M1:M5 type the country names 'Germany', 'Japan', 'Brazil', 'Kenya', 'Italy'. Select them, then Data → Data Types → Geography. Use the card icon to extract Population into N1:N5.</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>2.15 Linked Data Types</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>After conversion the cells show a map icon. Type =M1.Population in N1 and fill down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Self-check:</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Right-click any sheet tab → Unhide → Solutions to reveal the answer key. Try every task FIRST without peeking.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Solutions — Module 2 — Manage &amp; Format Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>These are the expected formulas / results for each Tasks sheet item. Try the task FIRST in real Excel, then peek here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Expected solution / formula</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Where it lands</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="14">
+        <f>LEFT(B2, FIND(",", B2)-1)  ← OR just type "Maria" in I2 and press Ctrl+E.</f>
+        <v/>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Raw Sales!I2:I51</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Column I should contain first names extracted from 'last, first' format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>[Green]$#,##0.00;[Red]($#,##0.00);"-"</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Raw Sales!G2:G51</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Negative test values render red in parens; zero shows '-'; positives green.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Data → Data Validation → Allow: Whole number, Between 1–100, Error Alert: Stop.</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Raw Sales!F2:F51</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Typing 200 in column F should pop a Stop alert and reject the entry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Select A1:H51 → Ctrl+T (header row checked) → Table Design → Table Name: tblSales.</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Raw Sales!A1:H51</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Name Box dropdown lists tblSales; Table Design ribbon appears when active inside it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Data → Remove Duplicates → check ONLY 'Customer (last, first)', 'Order Date', 'Product'.</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Raw Sales rows</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Excel reports '3 duplicates removed; 47 unique values remain'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Home → Conditional Formatting → Data Bars → any gradient.</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Raw Sales!F2:F51</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Larger quantity = longer bar inside the cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Build criteria range K20:L21 with headers Region/Status and values North/Shipped. Data → Advanced → Copy to another location → List range A1:H51 → Criteria K20:L21 → Copy to K1.</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Raw Sales!K1:R??</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Result block contains only rows where Region='North' AND Status='Shipped'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Data → Sort by Region first. Then Data → Subtotal: At each change in Region, Use SUM, Add subtotal to Quantity. Use the (1)(2)(3) outline buttons to collapse.</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Raw Sales (with outline)</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Each region group ends in a Total row showing SUM of Quantity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Formulas → Define Name → Name: NorthTarget → Refers to: =Targets!$B$4. Then in any free cell: =NorthTarget</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Workbook scope</t>
+        </is>
+      </c>
+      <c r="D13" s="8">
+        <f>NorthTarget returns 12000 from anywhere in the workbook.</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Select Targets!A3:C8 → Ctrl+T → My table has headers → Table Design → Table Name: tblTargets</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Targets!A3:C8</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>tblTargets shows up in Name Box; structured refs like tblTargets[Q1 Target ($)] resolve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Power Query M (illustrative):
+let Source = Excel.CurrentWorkbook(){[Name="tblSales"]}[Content],
+  Filtered = Table.SelectRows(Source, each [Status] &lt;&gt; "Cancelled"),
+  Added = Table.AddColumn(Filtered, "Revenue", each [Quantity]*[Unit Price], type number),
+  Grouped = Table.Group(Added, {"Region"}, {{"Total Revenue", each List.Sum([Revenue]), type number}})
+in Grouped</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>New sheet from Close &amp; Load</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Output has 5 region rows; 'Cancelled' rows excluded; totals match a SUMIFS sanity check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Type country names in M1:M5 → Select → Data → Data Types → Geography → click the card icon (or =M1.Population) for N1:N5.</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Raw Sales!M1:N5 (or any sheet)</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Cells show the linked-data icon; population is a numeric value, not a string.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
